--- a/output/full_scan/batch_seq8_2026-07-06.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6996</v>
+        <v>7795</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>808.5576953431956</v>
+        <v>929.4545341602886</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>199.5</v>
+        <v>666</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.56628181920126</v>
+        <v>82.44704176180485</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.67755559882237</v>
+        <v>32.24124881495894</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.4432017358025692</v>
+        <v>0.5454534160288679</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0229429641142</v>
+        <v>25.82768461740065</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8016</v>
+        <v>7610</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>782.1171386998711</v>
+        <v>884.1264995180443</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>332</v>
+        <v>2545</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.25130512857311</v>
+        <v>70.78571491192162</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>35.66534416809142</v>
+        <v>45.16888448379216</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5836273516341377</v>
+        <v>0.3201602666353436</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.27847490536378</v>
+        <v>4.273892390711353</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7738</v>
+        <v>8033</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>751.3773676296415</v>
+        <v>833.8065581379585</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>176.5</v>
+        <v>222</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.82173125356348</v>
+        <v>87.39907891918212</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.48409173258088</v>
+        <v>30.72146487742058</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.932577098197912</v>
+        <v>0.9806558137958568</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.6303928490384628</v>
+        <v>9.150297258718686</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7820</v>
+        <v>6996</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>750.2563296335649</v>
+        <v>808.5576953431956</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>126.5</v>
+        <v>199.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.19091859022676</v>
+        <v>56.56628181920126</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.06675152410525</v>
+        <v>20.67755559882237</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.103030526776235</v>
+        <v>0.4432017358025692</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.158907778825919</v>
+        <v>0.0229429641142</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8028</v>
+        <v>8016</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>739.8306055888596</v>
+        <v>782.1171386998711</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>330.5</v>
+        <v>332</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>58.95894638938504</v>
+        <v>61.25130512857311</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>31.00198444601112</v>
+        <v>35.66534416809142</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.739905732936121</v>
+        <v>0.5836273516341377</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2243838652252234</v>
+        <v>1.27847490536378</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6918</v>
+        <v>7738</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>730.9718468783749</v>
+        <v>751.3773676296415</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>75.5</v>
+        <v>176.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.70678373358305</v>
+        <v>62.82173125356348</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>9.016764460934382</v>
+        <v>22.48409173258088</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.056458334652158</v>
+        <v>1.932577098197912</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1738106105716678</v>
+        <v>0.6303928490384628</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8042</v>
+        <v>7820</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>684.731105436293</v>
+        <v>750.2563296335649</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>189.5</v>
+        <v>126.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>56.59515436379088</v>
+        <v>56.19091859022676</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.77310583162288</v>
+        <v>26.06675152410525</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.470343857885018</v>
+        <v>4.103030526776235</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.266236174743057</v>
+        <v>2.158907778825919</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6949</v>
+        <v>8028</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>675.6781873328719</v>
+        <v>739.8306055888596</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>891</v>
+        <v>330.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>62.30925460503114</v>
+        <v>58.95894638938504</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35.90649555956283</v>
+        <v>31.00198444601112</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.468493235513012</v>
+        <v>1.739905732936121</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3.54891441229443</v>
+        <v>0.2243838652252234</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7799</v>
+        <v>6918</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>667.6746140949479</v>
+        <v>730.9718468783749</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>430</v>
+        <v>75.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.06725860857528</v>
+        <v>60.70678373358305</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.48681809646846</v>
+        <v>9.016764460934382</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.353454803603822</v>
+        <v>2.056458334652158</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.760987467504599</v>
+        <v>0.1738106105716678</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8046</v>
+        <v>8042</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>647.7377324350057</v>
+        <v>684.731105436293</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1075</v>
+        <v>189.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.29605925317216</v>
+        <v>56.59515436379088</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.40943545421025</v>
+        <v>30.77310583162288</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.7454609317189949</v>
+        <v>2.470343857885018</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>17.6980541213933</v>
+        <v>-1.266236174743057</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7818</v>
+        <v>6949</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>636.0537097234728</v>
+        <v>675.6781873328719</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>70.5</v>
+        <v>891</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.65991324263209</v>
+        <v>62.30925460503114</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>37.14231824983066</v>
+        <v>35.90649555956283</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.213279023614598</v>
+        <v>0.468493235513012</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.928722700079517</v>
+        <v>3.54891441229443</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6870</v>
+        <v>7799</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>600.7847290794457</v>
+        <v>667.6746140949479</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>298</v>
+        <v>430</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.64887320439679</v>
+        <v>63.06725860857528</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.6897655206213</v>
+        <v>36.48681809646846</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3046721522845019</v>
+        <v>1.353454803603822</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.7372534224210678</v>
+        <v>2.760987467504599</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7753</v>
+        <v>8046</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>593.1528483002818</v>
+        <v>647.7377324350057</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>44.7</v>
+        <v>1075</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.79741514751806</v>
+        <v>57.29605925317216</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21.65412692090095</v>
+        <v>22.40943545421025</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.011419036089389</v>
+        <v>0.7454609317189949</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0869305598808129</v>
+        <v>17.6980541213933</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7788</v>
+        <v>7818</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>591.023598744369</v>
+        <v>636.0537097234728</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>239</v>
+        <v>70.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>48.33816490803895</v>
+        <v>58.65991324263209</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.69950384036846</v>
+        <v>37.14231824983066</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5128146450006684</v>
+        <v>2.213279023614598</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-5.9782958109509</v>
+        <v>1.928722700079517</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7715</v>
+        <v>6870</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>587.4908001176401</v>
+        <v>600.7847290794457</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>34.55</v>
+        <v>298</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>57.78154187556553</v>
+        <v>57.64887320439679</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45.56856977152104</v>
+        <v>22.6897655206213</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4038800913754483</v>
+        <v>0.3046721522845019</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.137876958461045</v>
+        <v>0.7372534224210678</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8044</v>
+        <v>7753</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>578.2968229196669</v>
+        <v>593.1528483002818</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>28.05</v>
+        <v>44.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46.98822290031948</v>
+        <v>60.79741514751806</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.27999465078208</v>
+        <v>21.65412692090095</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2274111996634095</v>
+        <v>1.011419036089389</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.3829853341179591</v>
+        <v>0.0869305598808129</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6916</v>
+        <v>7788</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>570.0430007874966</v>
+        <v>591.023598744369</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21.05</v>
+        <v>239</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.7375338816252</v>
+        <v>48.33816490803895</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.16621432313336</v>
+        <v>31.69950384036846</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.3198077337474104</v>
+        <v>0.5128146450006684</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.1286476927148785</v>
+        <v>-5.9782958109509</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7722</v>
+        <v>7715</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>538.176988967641</v>
+        <v>587.4908001176401</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>317</v>
+        <v>34.55</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>52.60654501903993</v>
+        <v>57.78154187556553</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>34.89128440875616</v>
+        <v>45.56856977152104</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.302903872002056</v>
+        <v>0.4038800913754483</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-2.056431174842613</v>
+        <v>0.137876958461045</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6962</v>
+        <v>8044</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>531.4386658020444</v>
+        <v>578.2968229196669</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>39.25</v>
+        <v>28.05</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.06152581559775</v>
+        <v>46.98822290031948</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14.26597483390512</v>
+        <v>15.27999465078208</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9154132579718538</v>
+        <v>0.2274111996634095</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0743401598881582</v>
+        <v>-0.3829853341179591</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7556</v>
+        <v>6916</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>530.0119038120073</v>
+        <v>570.0430007874966</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>287.5</v>
+        <v>21.05</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.217766307877</v>
+        <v>55.7375338816252</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>13.64838576325964</v>
+        <v>22.16621432313336</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6536874566791133</v>
+        <v>0.3198077337474104</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.762799220949065</v>
+        <v>-0.1286476927148785</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8043</v>
+        <v>7722</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>519.8218642202297</v>
+        <v>538.176988967641</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>196</v>
+        <v>317</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.66774660228722</v>
+        <v>52.60654501903993</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.04323932368959</v>
+        <v>34.89128440875616</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5346610694251631</v>
+        <v>0.302903872002056</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-3.750550413966511</v>
+        <v>-2.056431174842613</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8040</v>
+        <v>6962</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>518.8158245828131</v>
+        <v>531.4386658020444</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>99</v>
+        <v>39.25</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>47.87421253675058</v>
+        <v>56.06152581559775</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>33.00828695181024</v>
+        <v>14.26597483390512</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3329628551128293</v>
+        <v>0.9154132579718538</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.366626170404671</v>
+        <v>0.0743401598881582</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6901</v>
+        <v>7556</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>512.5159011757204</v>
+        <v>530.0119038120073</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>18.9</v>
+        <v>287.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>66.89670529369548</v>
+        <v>55.217766307877</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>49.09871573155542</v>
+        <v>13.64838576325964</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.327588027039728</v>
+        <v>0.6536874566791133</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.09426153072054889</v>
+        <v>0.762799220949065</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6928</v>
+        <v>8043</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>508.529982611409</v>
+        <v>519.8218642202297</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>57.1</v>
+        <v>196</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>69.74954396311233</v>
+        <v>55.66774660228722</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33.06641123965754</v>
+        <v>32.04323932368959</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.049177844772871</v>
+        <v>0.5346610694251631</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.993166947496214</v>
+        <v>-3.750550413966511</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7704</v>
+        <v>8040</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>503.3372417955636</v>
+        <v>518.8158245828131</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>63.8</v>
+        <v>99</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.83866609338025</v>
+        <v>47.87421253675058</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10.9212372129968</v>
+        <v>33.00828695181024</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8444631423203048</v>
+        <v>0.3329628551128293</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2676457277058199</v>
+        <v>-1.366626170404671</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7768</v>
+        <v>6901</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>501.8025245865275</v>
+        <v>512.5159011757204</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>370</v>
+        <v>18.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>51.2656751705318</v>
+        <v>66.89670529369548</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.86244801393961</v>
+        <v>49.09871573155542</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.949912451223216</v>
+        <v>1.327588027039728</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.166686316825526</v>
+        <v>0.09426153072054889</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7631</v>
+        <v>6928</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>499.5056603784947</v>
+        <v>508.529982611409</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>154.5</v>
+        <v>57.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.38274335203651</v>
+        <v>69.74954396311233</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>18.80674535259094</v>
+        <v>33.06641123965754</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7798499381317986</v>
+        <v>3.049177844772871</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.188827070880578</v>
+        <v>0.993166947496214</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7714</v>
+        <v>8021</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>469.7539410088858</v>
+        <v>508.4710354952899</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>151</v>
+        <v>530</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>61.87552027297598</v>
+        <v>52.11649287322791</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>30.77083578581708</v>
+        <v>22.48928704563725</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.662753139237959</v>
+        <v>0.09728045824672329</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.663656978268799</v>
+        <v>-5.509876892101531</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6906</v>
+        <v>7704</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>466.7033998431957</v>
+        <v>503.3372417955636</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>87.3</v>
+        <v>63.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.43939089018916</v>
+        <v>56.83866609338025</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.37112054475121</v>
+        <v>10.9212372129968</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8644149844648005</v>
+        <v>0.8444631423203048</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.8503296017991393</v>
+        <v>0.2676457277058199</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6894</v>
+        <v>7768</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>465.4541420688579</v>
+        <v>501.8025245865275</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>366.5</v>
+        <v>370</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.14026620649348</v>
+        <v>51.2656751705318</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.7532053796266</v>
+        <v>20.86244801393961</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.003616965869608</v>
+        <v>0.949912451223216</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.13534951756528</v>
+        <v>1.166686316825526</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7828</v>
+        <v>7631</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>459.8917902255869</v>
+        <v>499.5056603784947</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2035</v>
+        <v>154.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>54.39839993175939</v>
+        <v>55.38274335203651</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30.85156391907735</v>
+        <v>18.80674535259094</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.254713403643286</v>
+        <v>0.7798499381317986</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-17.45519331930217</v>
+        <v>1.188827070880578</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6936</v>
+        <v>7714</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>442.5554796113999</v>
+        <v>469.7539410088858</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>48.11347572286782</v>
+        <v>61.87552027297598</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>13.18956565592189</v>
+        <v>30.77083578581708</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.443098892542679</v>
+        <v>1.662753139237959</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0264305102448032</v>
+        <v>2.663656978268799</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6955</v>
+        <v>6906</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>441.445527500417</v>
+        <v>466.7033998431957</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>120.5</v>
+        <v>87.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>49.10519599722114</v>
+        <v>46.43939089018916</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>8.237986450793027</v>
+        <v>20.37112054475121</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.535115803513203</v>
+        <v>0.8644149844648005</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4897274204654467</v>
+        <v>-0.8503296017991393</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8039</v>
+        <v>6894</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>440.2798654149254</v>
+        <v>465.4541420688579</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>149.5</v>
+        <v>366.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.93997753537701</v>
+        <v>51.14026620649348</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.55991801443337</v>
+        <v>19.7532053796266</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.467987617856266</v>
+        <v>1.003616965869608</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.5007672579315279</v>
+        <v>-1.13534951756528</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6967</v>
+        <v>7828</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>440.0354827717049</v>
+        <v>459.8917902255869</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>73.3</v>
+        <v>2035</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.88325575451931</v>
+        <v>54.39839993175939</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13.47634237605425</v>
+        <v>30.85156391907735</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.761817790276177</v>
+        <v>1.254713403643286</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3642298504479105</v>
+        <v>-17.45519331930217</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7751</v>
+        <v>6936</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>431.3980689319487</v>
+        <v>442.5554796113999</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1505</v>
+        <v>33</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.97049729868765</v>
+        <v>48.11347572286782</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.40610306733902</v>
+        <v>13.18956565592189</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.355771949920162</v>
+        <v>2.443098892542679</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>21.93943476532129</v>
+        <v>0.0264305102448032</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7734</v>
+        <v>6955</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>420.1436962923449</v>
+        <v>441.445527500417</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2955</v>
+        <v>120.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43.54320914266127</v>
+        <v>49.10519599722114</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14.90553529202129</v>
+        <v>8.237986450793027</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7935219854524334</v>
+        <v>1.535115803513203</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-18.02941951810949</v>
+        <v>0.4897274204654467</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6971</v>
+        <v>8039</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>420.1260829399831</v>
+        <v>440.2798654149254</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>27.65</v>
+        <v>149.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.43952742181973</v>
+        <v>53.93997753537701</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.69862958976712</v>
+        <v>18.55991801443337</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6251137615117457</v>
+        <v>1.467987617856266</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0384230584977388</v>
+        <v>0.5007672579315279</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7402</v>
+        <v>6967</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>419.0865993814589</v>
+        <v>440.0354827717049</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>136</v>
+        <v>73.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>77.02239307224582</v>
+        <v>54.88325575451931</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30.09480656594014</v>
+        <v>13.47634237605425</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>6.03084472736673</v>
+        <v>1.761817790276177</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>4.98945527787203</v>
+        <v>0.3642298504479105</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6994</v>
+        <v>7751</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>418.4491264816116</v>
+        <v>431.3980689319487</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>46.05</v>
+        <v>1505</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>36.94824114989741</v>
+        <v>49.97049729868765</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>32.17878478539778</v>
+        <v>11.40610306733902</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9449126481611588</v>
+        <v>1.355771949920162</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.7397067737007896</v>
+        <v>21.93943476532129</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8032</v>
+        <v>7734</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>417.7145098502771</v>
+        <v>420.1436962923449</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>43.05</v>
+        <v>2955</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45.84916858244169</v>
+        <v>43.54320914266127</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.44919255581133</v>
+        <v>14.90553529202129</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2513387039414778</v>
+        <v>0.7935219854524334</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.4419131521041536</v>
+        <v>-18.02941951810949</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6909</v>
+        <v>6971</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>412.8882902648648</v>
+        <v>420.1260829399831</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>57.6</v>
+        <v>27.65</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.07563475292047</v>
+        <v>49.43952742181973</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.62417394626726</v>
+        <v>21.69862958976712</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8720555619241196</v>
+        <v>0.6251137615117457</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.7401126215434355</v>
+        <v>0.0384230584977388</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7760</v>
+        <v>7402</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>406.4008044477481</v>
+        <v>419.0865993814589</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>36.7</v>
+        <v>136</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>73.5528826865918</v>
+        <v>77.02239307224582</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>37.14755146912424</v>
+        <v>30.09480656594014</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7180696513662335</v>
+        <v>6.03084472736673</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.5400392125542108</v>
+        <v>4.98945527787203</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6944</v>
+        <v>6994</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>404.3488926975456</v>
+        <v>418.4491264816116</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>981</v>
+        <v>46.05</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.01118570314598</v>
+        <v>36.94824114989741</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.72630009756846</v>
+        <v>32.17878478539778</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4413343259492023</v>
+        <v>0.9449126481611588</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-5.198695742201618</v>
+        <v>-0.7397067737007896</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6924</v>
+        <v>8032</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>375.3649140663555</v>
+        <v>417.7145098502771</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>129.5</v>
+        <v>43.05</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>50.75655082205656</v>
+        <v>45.84916858244169</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.82970850389795</v>
+        <v>19.44919255581133</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.06302661042939</v>
+        <v>0.2513387039414778</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1742396227848717</v>
+        <v>-0.4419131521041536</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7770</v>
+        <v>6909</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>367.5212963749695</v>
+        <v>412.8882902648648</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>43.15</v>
+        <v>57.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.59790170091334</v>
+        <v>56.07563475292047</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5.767068536353909</v>
+        <v>19.62417394626726</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3.360505657263016</v>
+        <v>0.8720555619241196</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1134612889817984</v>
+        <v>0.7401126215434355</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6983</v>
+        <v>7760</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>365.9467187988611</v>
+        <v>406.4008044477481</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>353</v>
+        <v>36.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45.12023014575066</v>
+        <v>73.5528826865918</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10.9487767005768</v>
+        <v>37.14755146912424</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.085864679449504</v>
+        <v>0.7180696513662335</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.455772388096385</v>
+        <v>0.5400392125542108</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6863</v>
+        <v>6944</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>365.2708837618432</v>
+        <v>404.3488926975456</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>981</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>39.91768101875077</v>
+        <v>51.01118570314598</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>23.36266745349691</v>
+        <v>13.72630009756846</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7159363759266344</v>
+        <v>0.4413343259492023</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0384723670537061</v>
+        <v>-5.198695742201618</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7821</v>
+        <v>6924</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>365.1368595020265</v>
+        <v>375.3649140663555</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>42.05</v>
+        <v>129.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>38.18562502532784</v>
+        <v>50.75655082205656</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.80168195406543</v>
+        <v>18.82970850389795</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5977253596690894</v>
+        <v>1.06302661042939</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0167894449167005</v>
+        <v>0.1742396227848717</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6862</v>
+        <v>7770</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>364.1966498705082</v>
+        <v>367.5212963749695</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>195</v>
+        <v>43.15</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.75090648188154</v>
+        <v>51.59790170091334</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.12488486744902</v>
+        <v>5.767068536353909</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4917852905554007</v>
+        <v>3.360505657263016</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.714025409961317</v>
+        <v>0.1134612889817984</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7772</v>
+        <v>6983</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>364.0929430650338</v>
+        <v>365.9467187988611</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>137</v>
+        <v>353</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.49095251673181</v>
+        <v>45.12023014575066</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>8.924651822535129</v>
+        <v>10.9487767005768</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.394567499830658</v>
+        <v>1.085864679449504</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2307460817962443</v>
+        <v>2.455772388096385</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7823</v>
+        <v>6863</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>362.3755040127487</v>
+        <v>365.2708837618432</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>80</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>35.27558701800362</v>
+        <v>39.91768101875077</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>29.32513746045671</v>
+        <v>23.36266745349691</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.268671301337354</v>
+        <v>0.7159363759266344</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1504065040479703</v>
+        <v>0.0384723670537061</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6890</v>
+        <v>7821</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>360.1219113909337</v>
+        <v>365.1368595020265</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>212.5</v>
+        <v>42.05</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.14948019372937</v>
+        <v>38.18562502532784</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.06019099023955</v>
+        <v>23.80168195406543</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.944978314929384</v>
+        <v>0.5977253596690894</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-5.907118004127213</v>
+        <v>0.0167894449167005</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7822</v>
+        <v>6862</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>358.3837578194981</v>
+        <v>364.1966498705082</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1120</v>
+        <v>195</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.94393567060128</v>
+        <v>49.75090648188154</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.56588219494362</v>
+        <v>21.12488486744902</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7878885997529143</v>
+        <v>0.4917852905554007</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>5.679528100395556</v>
+        <v>-1.714025409961317</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6854</v>
+        <v>7772</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>353.9492334346256</v>
+        <v>364.0929430650338</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>121.5</v>
+        <v>137</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>36.73641125524091</v>
+        <v>45.49095251673181</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.15987657513313</v>
+        <v>8.924651822535129</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6317619862798323</v>
+        <v>1.394567499830658</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1117305075682981</v>
+        <v>0.2307460817962443</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6969</v>
+        <v>7823</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>349.4071921220389</v>
+        <v>362.3755040127487</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>25.6</v>
+        <v>80</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.09133029185336</v>
+        <v>35.27558701800362</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>29.93176405922842</v>
+        <v>29.32513746045671</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.855805818919737</v>
+        <v>1.268671301337354</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0379958137027598</v>
+        <v>0.1504065040479703</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6951</v>
+        <v>6890</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>348.6677615716242</v>
+        <v>360.1219113909337</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>79.40000000000001</v>
+        <v>212.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.70853929021337</v>
+        <v>49.14948019372937</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.64979098130871</v>
+        <v>22.06019099023955</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3593501270766907</v>
+        <v>0.944978314929384</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1638260920623528</v>
+        <v>-5.907118004127213</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7711</v>
+        <v>7822</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>347.9809735116742</v>
+        <v>358.3837578194981</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>325</v>
+        <v>1120</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.95837231880899</v>
+        <v>47.94393567060128</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.91966806332578</v>
+        <v>18.56588219494362</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4257042849730579</v>
+        <v>0.7878885997529143</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.269558689302379</v>
+        <v>5.679528100395556</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7747</v>
+        <v>6854</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>347.8126971989092</v>
+        <v>353.9492334346256</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>131</v>
+        <v>121.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.77392738369171</v>
+        <v>36.73641125524091</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4.219617326352378</v>
+        <v>21.15987657513313</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.0854070504261875</v>
+        <v>0.6317619862798323</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2210617519179032</v>
+        <v>0.1117305075682981</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6902</v>
+        <v>6969</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>344.3414706069329</v>
+        <v>349.4071921220389</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>132.5</v>
+        <v>25.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.59855644784968</v>
+        <v>46.09133029185336</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.07582619398515</v>
+        <v>29.93176405922842</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1352170456411022</v>
+        <v>2.855805818919737</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.8791197212018802</v>
+        <v>0.0379958137027598</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6903</v>
+        <v>6951</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>341.2491858082841</v>
+        <v>348.6677615716242</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>392.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.57310864033495</v>
+        <v>51.70853929021337</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>9.554426668286585</v>
+        <v>23.64979098130871</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8197390888423756</v>
+        <v>0.3593501270766907</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.760233401497221</v>
+        <v>0.1638260920623528</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6914</v>
+        <v>7711</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>338.2840444581312</v>
+        <v>347.9809735116742</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>144.5</v>
+        <v>325</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>57.38404577396695</v>
+        <v>38.95837231880899</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.13756676489917</v>
+        <v>20.91966806332578</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.391249559576364</v>
+        <v>0.4257042849730579</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3692128923551344</v>
+        <v>-2.269558689302379</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7717</v>
+        <v>7747</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>336.0761667203516</v>
+        <v>347.8126971989092</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>450.5</v>
+        <v>131</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>35.40462923591558</v>
+        <v>53.77392738369171</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.11061458992054</v>
+        <v>4.219617326352378</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7327460644240542</v>
+        <v>0.0854070504261875</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.268946289748506</v>
+        <v>0.2210617519179032</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6861</v>
+        <v>6902</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>334.2754433270309</v>
+        <v>344.3414706069329</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>321.5</v>
+        <v>132.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.94377433710053</v>
+        <v>50.59855644784968</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.91628506885554</v>
+        <v>21.07582619398515</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5339688657381355</v>
+        <v>0.1352170456411022</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.80902299173864</v>
+        <v>-0.8791197212018802</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7750</v>
+        <v>6903</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>333.5995046130093</v>
+        <v>341.2491858082841</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>2190</v>
+        <v>392.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.83089189729845</v>
+        <v>50.57310864033495</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>17.59234014727713</v>
+        <v>9.554426668286585</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4044697375337109</v>
+        <v>0.8197390888423756</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>4.856941648578768</v>
+        <v>1.760233401497221</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7805</v>
+        <v>6914</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>332.4900188086705</v>
+        <v>338.2840444581312</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>662</v>
+        <v>144.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>37.24215626134557</v>
+        <v>57.38404577396695</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>27.4146123673331</v>
+        <v>11.13756676489917</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.290735733598976</v>
+        <v>1.391249559576364</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.1991319947793</v>
+        <v>0.3692128923551344</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6953</v>
+        <v>7717</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>330.4783710019182</v>
+        <v>336.0761667203516</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>237.5</v>
+        <v>450.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.04611946419537</v>
+        <v>35.40462923591558</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14.41988182174156</v>
+        <v>22.11061458992054</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7082254722890194</v>
+        <v>0.7327460644240542</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.75443267842113</v>
+        <v>-2.268946289748506</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7827</v>
+        <v>6861</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>326.7621793358026</v>
+        <v>334.2754433270309</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>156</v>
+        <v>321.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.3170645042681</v>
+        <v>44.94377433710053</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.44683477943262</v>
+        <v>15.91628506885554</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.501636522807291</v>
+        <v>0.5339688657381355</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.631219594587102</v>
+        <v>-1.80902299173864</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7810</v>
+        <v>7750</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>320.9487647221342</v>
+        <v>333.5995046130093</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>204.5</v>
+        <v>2190</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.9177883561323</v>
+        <v>49.83089189729845</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.23542710644914</v>
+        <v>17.59234014727713</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9296257616585664</v>
+        <v>0.4044697375337109</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.090814967273589</v>
+        <v>4.856941648578768</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8047</v>
+        <v>7805</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>316.0419753962674</v>
+        <v>332.4900188086705</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>44.7</v>
+        <v>662</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>40.81769989697366</v>
+        <v>37.24215626134557</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6.025167843423358</v>
+        <v>27.4146123673331</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.1910859366877538</v>
+        <v>1.290735733598976</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.4068721231688827</v>
+        <v>-1.1991319947793</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6919</v>
+        <v>6953</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>309.2147303449316</v>
+        <v>330.4783710019182</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>100</v>
+        <v>237.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.16151000441005</v>
+        <v>50.04611946419537</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.35795178573436</v>
+        <v>14.41988182174156</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5380468887251496</v>
+        <v>0.7082254722890194</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.139289998133207</v>
+        <v>1.75443267842113</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7705</v>
+        <v>7827</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>303.7362301071217</v>
+        <v>326.7621793358026</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>31.2</v>
+        <v>156</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.93961722569053</v>
+        <v>46.3170645042681</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.0544360864461</v>
+        <v>18.44683477943262</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.970284329907041</v>
+        <v>0.501636522807291</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0691775224885767</v>
+        <v>-1.631219594587102</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6965</v>
+        <v>7810</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>302.780622352246</v>
+        <v>320.9487647221342</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>79</v>
+        <v>204.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.67385371873763</v>
+        <v>44.9177883561323</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>23.90718729584355</v>
+        <v>12.23542710644914</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.61121152946113</v>
+        <v>0.9296257616585664</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1357554151498277</v>
+        <v>1.090814967273589</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6859</v>
+        <v>8047</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>301.3352845634572</v>
+        <v>316.0419753962674</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>122</v>
+        <v>44.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.89805549745337</v>
+        <v>40.81769989697366</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.69437390104593</v>
+        <v>6.025167843423358</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4231016763473422</v>
+        <v>0.1910859366877538</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.216224416098218</v>
+        <v>-0.4068721231688827</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6887</v>
+        <v>6919</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>299.5307231390944</v>
+        <v>309.2147303449316</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.06344778274436</v>
+        <v>50.16151000441005</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5.610104599147776</v>
+        <v>13.35795178573436</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.169509517894797</v>
+        <v>0.5380468887251496</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0859210190626655</v>
+        <v>-0.139289998133207</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7703</v>
+        <v>7705</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>292.388518883964</v>
+        <v>303.7362301071217</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>200</v>
+        <v>31.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.0462527574199</v>
+        <v>42.93961722569053</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.22820973729434</v>
+        <v>18.0544360864461</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9403850216769702</v>
+        <v>1.970284329907041</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.2746825173970222</v>
+        <v>0.0691775224885767</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7728</v>
+        <v>6965</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>292.2540566831527</v>
+        <v>302.780622352246</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>680</v>
+        <v>79</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.20016801402379</v>
+        <v>47.67385371873763</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.7943327588782</v>
+        <v>23.90718729584355</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.7198402955037209</v>
+        <v>0.61121152946113</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.782269863182783</v>
+        <v>-0.1357554151498277</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7547</v>
+        <v>6859</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>292.1007781444015</v>
+        <v>301.3352845634572</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>58.5</v>
+        <v>122</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.99350258846889</v>
+        <v>44.89805549745337</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.06410074554698</v>
+        <v>18.69437390104593</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.1833950029441484</v>
+        <v>0.4231016763473422</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.4207045922654275</v>
+        <v>-1.216224416098218</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6923</v>
+        <v>6887</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>288.3535527440473</v>
+        <v>299.5307231390944</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>34</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>55.812595251954</v>
+        <v>46.06344778274436</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.21874399643354</v>
+        <v>5.610104599147776</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.040643344145244</v>
+        <v>2.169509517894797</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.199542256402375</v>
+        <v>-0.0859210190626655</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6913</v>
+        <v>7703</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>286.8088554354494</v>
+        <v>292.388518883964</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.17660465751025</v>
+        <v>46.0462527574199</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.38168602218034</v>
+        <v>11.22820973729434</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8497917136776261</v>
+        <v>0.9403850216769702</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2347095338749332</v>
+        <v>-0.2746825173970222</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7780</v>
+        <v>7728</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>285.2315361933975</v>
+        <v>292.2540566831527</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18.35</v>
+        <v>680</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.0400026707871</v>
+        <v>45.20016801402379</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.58660452980001</v>
+        <v>10.7943327588782</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5449104093329594</v>
+        <v>0.7198402955037209</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0055792192090978</v>
+        <v>-1.782269863182783</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6937</v>
+        <v>7547</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>283.7772923417312</v>
+        <v>292.1007781444015</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>275</v>
+        <v>58.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>47.61527460885561</v>
+        <v>43.99350258846889</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.07732438393498</v>
+        <v>13.06410074554698</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.0405201027363</v>
+        <v>0.1833950029441484</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>2.094179548407443</v>
+        <v>0.4207045922654275</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7786</v>
+        <v>6923</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>283.4576476512762</v>
+        <v>288.3535527440473</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>124</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.55057940595168</v>
+        <v>55.812595251954</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.35068925163295</v>
+        <v>13.21874399643354</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7131092655467695</v>
+        <v>1.040643344145244</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0739229952286302</v>
+        <v>0.199542256402375</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8045</v>
+        <v>6913</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>281.6812566631756</v>
+        <v>286.8088554354494</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>61.4</v>
+        <v>125</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.78650533239862</v>
+        <v>49.17660465751025</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>11.03922802673121</v>
+        <v>16.38168602218034</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8188933563814492</v>
+        <v>0.8497917136776261</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.3974591265122988</v>
+        <v>0.2347095338749332</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6922</v>
+        <v>7780</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>278.5775687627349</v>
+        <v>285.2315361933975</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>180.5</v>
+        <v>18.35</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.53365996994474</v>
+        <v>49.0400026707871</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.80465333673044</v>
+        <v>14.58660452980001</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3846871395293277</v>
+        <v>0.5449104093329594</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.263390381166769</v>
+        <v>0.0055792192090978</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6873</v>
+        <v>6937</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>277.1604949454289</v>
+        <v>283.7772923417312</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>89.5</v>
+        <v>275</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>59.36211099082309</v>
+        <v>47.61527460885561</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.2004994062494</v>
+        <v>13.07732438393498</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.301462612452606</v>
+        <v>1.0405201027363</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.9459040702648522</v>
+        <v>2.094179548407443</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6997</v>
+        <v>7786</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>261.0245213790066</v>
+        <v>283.4576476512762</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>124</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>50.66773545312253</v>
+        <v>48.55057940595168</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>6.740523437290677</v>
+        <v>15.35068925163295</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.123562137440852</v>
+        <v>0.7131092655467695</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0346589355715896</v>
+        <v>-0.0739229952286302</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7749</v>
+        <v>8045</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>252.4982241945947</v>
+        <v>281.6812566631756</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>427</v>
+        <v>61.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.82399585559756</v>
+        <v>44.78650533239862</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.85410782059997</v>
+        <v>11.03922802673121</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3796903811447959</v>
+        <v>0.8188933563814492</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-4.950512184738159</v>
+        <v>0.3974591265122988</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6952</v>
+        <v>6922</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>246.9534089216984</v>
+        <v>278.5775687627349</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>35.4</v>
+        <v>180.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>36.08875985437926</v>
+        <v>48.53365996994474</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>20.2618036042714</v>
+        <v>14.80465333673044</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5924472336898055</v>
+        <v>0.3846871395293277</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0156673711332383</v>
+        <v>-0.263390381166769</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7792</v>
+        <v>6873</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>244.9657907111391</v>
+        <v>277.1604949454289</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>254.5</v>
+        <v>89.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.90823933243598</v>
+        <v>59.36211099082309</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.01461253726303</v>
+        <v>13.2004994062494</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5122422585717855</v>
+        <v>1.301462612452606</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2669754885868549</v>
+        <v>0.9459040702648522</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6933</v>
+        <v>6997</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>238.8593985580696</v>
+        <v>261.0245213790066</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>149</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.0900346488649</v>
+        <v>50.66773545312253</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.02320031181444</v>
+        <v>6.740523437290677</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6764081408017897</v>
+        <v>1.123562137440852</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.5303575432216681</v>
+        <v>0.0346589355715896</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6910</v>
+        <v>7749</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>231.124296050598</v>
+        <v>252.4982241945947</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>27.4</v>
+        <v>427</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>41.76225136824827</v>
+        <v>38.82399585559756</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.45944489502893</v>
+        <v>15.85410782059997</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.470588871137553</v>
+        <v>0.3796903811447959</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0589767343673025</v>
+        <v>-4.950512184738159</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6899</v>
+        <v>6952</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>230.7550723476388</v>
+        <v>246.9534089216984</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>59</v>
+        <v>35.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.31621737540953</v>
+        <v>36.08875985437926</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.38988764519294</v>
+        <v>20.2618036042714</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5642802424810111</v>
+        <v>0.5924472336898055</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2630043841779771</v>
+        <v>0.0156673711332383</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6865</v>
+        <v>7792</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>230.4422626311943</v>
+        <v>244.9657907111391</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>28.3</v>
+        <v>254.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.500523778252</v>
+        <v>41.90823933243598</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.98610457431443</v>
+        <v>19.01461253726303</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.092589290717637</v>
+        <v>0.5122422585717855</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.469613746995678</v>
+        <v>0.2669754885868549</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6855</v>
+        <v>6933</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>222.0001983422327</v>
+        <v>238.8593985580696</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>120.5</v>
+        <v>149</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.81232745570334</v>
+        <v>46.0900346488649</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9.620059414681419</v>
+        <v>20.02320031181444</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.357573410152751</v>
+        <v>0.6764081408017897</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.5350983884906486</v>
+        <v>0.5303575432216681</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7842</v>
+        <v>6910</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>221.2390041430416</v>
+        <v>231.124296050598</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>98.5</v>
+        <v>27.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.29061490908995</v>
+        <v>41.76225136824827</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>24.2684417198557</v>
+        <v>12.45944489502893</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7604071461957315</v>
+        <v>1.470588871137553</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.7949101018037634</v>
+        <v>-0.0589767343673025</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6934</v>
+        <v>6899</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>221.1465089357069</v>
+        <v>230.7550723476388</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.32390150393589</v>
+        <v>48.31621737540953</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>21.05416951521602</v>
+        <v>16.38988764519294</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6427079738686531</v>
+        <v>0.5642802424810111</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.3955706024865217</v>
+        <v>-0.2630043841779771</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7839</v>
+        <v>6865</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>213.9648511373288</v>
+        <v>230.4422626311943</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>42.3</v>
+        <v>28.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>41.88061065901555</v>
+        <v>51.500523778252</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>8.962160847713308</v>
+        <v>14.98610457431443</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4930289898034565</v>
+        <v>0.092589290717637</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3243931790042631</v>
+        <v>0.469613746995678</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6877</v>
+        <v>6855</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>209.4115283042462</v>
+        <v>222.0001983422327</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>133.5</v>
+        <v>120.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.66379749157642</v>
+        <v>51.81232745570334</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.36546274416084</v>
+        <v>9.620059414681419</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4994854049369263</v>
+        <v>1.357573410152751</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>1.383997480355861</v>
+        <v>0.5350983884906486</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7721</v>
+        <v>7842</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>208.4023140249882</v>
+        <v>221.2390041430416</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>71.5</v>
+        <v>98.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.22763671066135</v>
+        <v>39.29061490908995</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.6531988439668</v>
+        <v>24.2684417198557</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4850212102405107</v>
+        <v>0.7604071461957315</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.2567772583172402</v>
+        <v>0.7949101018037634</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7769</v>
+        <v>6934</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>207.340132102832</v>
+        <v>221.1465089357069</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>6800</v>
+        <v>68</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.69097893107295</v>
+        <v>45.32390150393589</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.37848545730475</v>
+        <v>21.05416951521602</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5084012436370695</v>
+        <v>0.6427079738686531</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-40.33412059007298</v>
+        <v>0.3955706024865217</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7744</v>
+        <v>7839</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>194.2989155678273</v>
+        <v>213.9648511373288</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>465</v>
+        <v>42.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>47.2301778964923</v>
+        <v>41.88061065901555</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>12.82460281482104</v>
+        <v>8.962160847713308</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.1653476881797353</v>
+        <v>0.4930289898034565</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>1.409276246264427</v>
+        <v>-0.3243931790042631</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7765</v>
+        <v>6877</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>183.4232678560222</v>
+        <v>209.4115283042462</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>225</v>
+        <v>133.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.21852639018771</v>
+        <v>46.66379749157642</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>24.67271990281701</v>
+        <v>15.36546274416084</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5080024059854685</v>
+        <v>0.4994854049369263</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-1.180098429624526</v>
+        <v>1.383997480355861</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7732</v>
+        <v>7721</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>181.2935372572812</v>
+        <v>208.4023140249882</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>35.45</v>
+        <v>71.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.68366689941129</v>
+        <v>45.22763671066135</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.41088897685778</v>
+        <v>12.6531988439668</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.452032118950471</v>
+        <v>0.4850212102405107</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>1.063220448953308</v>
+        <v>-0.2567772583172402</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7736</v>
+        <v>7769</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>168.0117675836741</v>
+        <v>207.340132102832</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>6800</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>39.509095631718</v>
+        <v>48.69097893107295</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.9931721700066</v>
+        <v>15.37848545730475</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.432247564167418</v>
+        <v>0.5084012436370695</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0539703592471046</v>
+        <v>-40.33412059007298</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6931</v>
+        <v>7744</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>160.5631203018051</v>
+        <v>194.2989155678273</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>40.2</v>
+        <v>465</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.63404063684898</v>
+        <v>47.2301778964923</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19.54343801679693</v>
+        <v>12.82460281482104</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.8242627494819144</v>
+        <v>0.1653476881797353</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1295020055014252</v>
+        <v>1.409276246264427</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6869</v>
+        <v>7765</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>159.1090688850164</v>
+        <v>183.4232678560222</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>72.7</v>
+        <v>225</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.37648381701112</v>
+        <v>41.21852639018771</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>27.45146617108549</v>
+        <v>24.67271990281701</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.242924851674807</v>
+        <v>0.5080024059854685</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.3514495373705761</v>
+        <v>-1.180098429624526</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7740</v>
+        <v>7732</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>158.5668026573883</v>
+        <v>181.2935372572812</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>145</v>
+        <v>35.45</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>37.09730509339733</v>
+        <v>51.68366689941129</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.3802687824269</v>
+        <v>12.41088897685778</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2857714209889902</v>
+        <v>1.452032118950471</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.7429292493930761</v>
+        <v>1.063220448953308</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7803</v>
+        <v>7736</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>150.1740128156908</v>
+        <v>168.0117675836741</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>23.35</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.71618293878065</v>
+        <v>39.509095631718</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.49787743598738</v>
+        <v>12.9931721700066</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8701522335847032</v>
+        <v>1.432247564167418</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.340568166117104</v>
+        <v>-0.0539703592471046</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8034</v>
+        <v>6931</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>147.8184512025872</v>
+        <v>160.5631203018051</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>22.25</v>
+        <v>40.2</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>38.15305784444094</v>
+        <v>43.63404063684898</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>22.60530995948744</v>
+        <v>19.54343801679693</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5585801721477769</v>
+        <v>0.8242627494819144</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.077971808575725</v>
+        <v>0.1295020055014252</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6921</v>
+        <v>6869</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>128.3431836382204</v>
+        <v>159.1090688850164</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>69</v>
+        <v>72.7</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.3053822315196</v>
+        <v>41.37648381701112</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.80291287299055</v>
+        <v>27.45146617108549</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.24539576201519</v>
+        <v>1.242924851674807</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.2851916724549008</v>
+        <v>-0.3514495373705761</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6925</v>
+        <v>7740</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>123.9568443996038</v>
+        <v>158.5668026573883</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>60.7</v>
+        <v>145</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.53244035032524</v>
+        <v>37.09730509339733</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.93587930828906</v>
+        <v>18.3802687824269</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.1781725439592989</v>
+        <v>0.2857714209889902</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2450011389061248</v>
+        <v>-0.7429292493930761</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6988</v>
+        <v>7803</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>117.6276673930864</v>
+        <v>150.1740128156908</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>13.5</v>
+        <v>23.35</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>34.35480693095018</v>
+        <v>46.71618293878065</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.44523754872059</v>
+        <v>15.49787743598738</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.170694960158196</v>
+        <v>0.8701522335847032</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0185172593522769</v>
+        <v>0.340568166117104</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6958</v>
+        <v>8034</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>92.41298837582256</v>
+        <v>147.8184512025872</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>16.85</v>
+        <v>22.25</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.80004274284517</v>
+        <v>38.15305784444094</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.44871671840606</v>
+        <v>22.60530995948744</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4985717108488989</v>
+        <v>0.5585801721477769</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0102254289892285</v>
+        <v>-0.077971808575725</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6895</v>
+        <v>6921</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>81.65318981779947</v>
+        <v>128.3431836382204</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>42.67305600774954</v>
+        <v>40.3053822315196</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.11126014373055</v>
+        <v>16.80291287299055</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.9047058802003188</v>
+        <v>0.24539576201519</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-1.070187937861062</v>
+        <v>0.2851916724549008</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7730</v>
+        <v>6925</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>79.6130477322164</v>
+        <v>123.9568443996038</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>190</v>
+        <v>60.7</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>53.34146863923446</v>
+        <v>44.53244035032524</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11.28862993539881</v>
+        <v>13.93587930828906</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5949000528810644</v>
+        <v>0.1781725439592989</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>1.394097270453536</v>
+        <v>-0.2450011389061248</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6908</v>
+        <v>6988</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>78.35031173016577</v>
+        <v>117.6276673930864</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>37.5</v>
+        <v>13.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.31813360437424</v>
+        <v>34.35480693095018</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.77258554856808</v>
+        <v>13.44523754872059</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6735955418346955</v>
+        <v>1.170694960158196</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0350618122122836</v>
+        <v>0.0185172593522769</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>7791</v>
+        <v>6958</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>76.56842712732785</v>
+        <v>92.41298837582256</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>62.7</v>
+        <v>16.85</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.32601324148337</v>
+        <v>46.80004274284517</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.91289426187235</v>
+        <v>14.44871671840606</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6502092840283241</v>
+        <v>0.4985717108488989</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0852175223236462</v>
+        <v>0.0102254289892285</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6885</v>
+        <v>6895</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>73.59000142663271</v>
+        <v>81.65318981779947</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>21.75</v>
+        <v>148</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.38861742178057</v>
+        <v>42.67305600774954</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.59963410419549</v>
+        <v>16.11126014373055</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3734579037725326</v>
+        <v>0.9047058802003188</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0268683865490492</v>
+        <v>-1.070187937861062</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,52 +6993,264 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
+        <v>7730</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>暉盛-創</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>79.6130477322164</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>53.34146863923446</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>11.28862993539881</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.5949000528810644</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>1.394097270453536</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6908</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>宏碁遊戲-創</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>78.35031173016577</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>41.31813360437424</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>12.77258554856808</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.6735955418346955</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.0350618122122836</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>7791</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>皇家可口</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>76.56842712732785</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>46.32601324148337</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>14.91289426187235</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.6502092840283241</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.0852175223236462</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6885</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>全福生技</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>73.59000142663271</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>46.38861742178057</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>17.59963410419549</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.3734579037725326</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.0268683865490492</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>8011</v>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>台通</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D124" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>15.7123161271514</v>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>17.95</v>
       </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H124" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>49.08642828556086</v>
       </c>
-      <c r="I124" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>14.60956115700132</v>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>1.140581474166339</v>
       </c>
-      <c r="K124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N124" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>0.0582058160686841</v>
       </c>
-      <c r="O124" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60</t>
         </is>
